--- a/data/department_schedules_midterms/Gıda Mühendisliği.xlsx
+++ b/data/department_schedules_midterms/Gıda Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_midterms\modified\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_midterms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F67C67-35FA-4657-BDB2-E437E2249A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{71F67C67-35FA-4657-BDB2-E437E2249A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B88F868-3431-4831-8490-BFA5F6991347}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
   <si>
     <t>Year:</t>
   </si>
@@ -242,6 +242,48 @@
   </si>
   <si>
     <t>Rooms Used</t>
+  </si>
+  <si>
+    <t>C206</t>
+  </si>
+  <si>
+    <t>C206,C207</t>
+  </si>
+  <si>
+    <t>C206,C207,C211</t>
+  </si>
+  <si>
+    <t>C206,C208</t>
+  </si>
+  <si>
+    <t>C205,C206,C207</t>
+  </si>
+  <si>
+    <t>C207,C210,C211</t>
+  </si>
+  <si>
+    <t>C207,C206,C211,C210</t>
+  </si>
+  <si>
+    <t>B102,C206</t>
+  </si>
+  <si>
+    <t>B102,C205,C206</t>
+  </si>
+  <si>
+    <t>B102,C208</t>
+  </si>
+  <si>
+    <t>C207</t>
+  </si>
+  <si>
+    <t>B102,C207,C208</t>
+  </si>
+  <si>
+    <t>C208</t>
+  </si>
+  <si>
+    <t>C206,C207,C210</t>
   </si>
 </sst>
 </file>
@@ -322,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -330,25 +372,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -361,6 +391,35 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -391,35 +450,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -434,14 +464,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FC2381AD-6778-41F9-ACAC-AF3D65D9629E}" name="Table1" displayName="Table1" ref="A1:F35" totalsRowShown="0" headerRowDxfId="2" dataDxfId="1" headerRowBorderDxfId="8" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FC2381AD-6778-41F9-ACAC-AF3D65D9629E}" name="Table1" displayName="Table1" ref="A1:F35" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
   <autoFilter ref="A1:F35" xr:uid="{FC2381AD-6778-41F9-ACAC-AF3D65D9629E}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7D1FAC21-C77B-4280-8CD4-F6E89E906E16}" name="Year:" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{4341507C-2811-4BA6-983D-68DAB00CF0AC}" name="Course ID" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{7066E1F9-34A6-48B3-B554-2B2C81BCB854}" name="Date" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{BB1BA36B-DC26-4A18-9F1E-042D10FD23EC}" name="Rooms" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{4184EE83-9F6D-4BDA-9EF8-4D1266889DD2}" name="Course Name" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{7D1FAC21-C77B-4280-8CD4-F6E89E906E16}" name="Year:" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{4341507C-2811-4BA6-983D-68DAB00CF0AC}" name="Course ID" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{7066E1F9-34A6-48B3-B554-2B2C81BCB854}" name="Date" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{BB1BA36B-DC26-4A18-9F1E-042D10FD23EC}" name="Rooms" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{4184EE83-9F6D-4BDA-9EF8-4D1266889DD2}" name="Course Name" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{58001B5B-8A30-41D8-8317-3016B5EA3FBB}" name="Rooms Used" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -736,14 +766,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="39.90625" customWidth="1"/>
-    <col min="6" max="6" width="22.36328125" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="39.9296875" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -763,7 +793,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -779,9 +809,11 @@
       <c r="E2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F2" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -797,9 +829,11 @@
       <c r="E3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F3" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -815,9 +849,11 @@
       <c r="E4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F4" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -833,9 +869,11 @@
       <c r="E5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F5" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -851,9 +889,11 @@
       <c r="E6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F6" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -864,516 +904,574 @@
         <v>3</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
-        <v>2</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="F7" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="3">
+        <v>2</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>6</v>
       </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="D8" s="3">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="F8" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="3">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>9</v>
       </c>
-      <c r="D9" s="4">
-        <v>2</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
-        <v>2</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="F9" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="3">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>7</v>
       </c>
-      <c r="D10" s="4">
-        <v>2</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>2</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="F10" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="3">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>9</v>
       </c>
-      <c r="D11" s="4">
-        <v>3</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>2</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="F11" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" s="3">
+        <v>2</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>8</v>
       </c>
-      <c r="D12" s="4">
-        <v>2</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="D12" s="3">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
-        <v>2</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="F12" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="3">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>7</v>
       </c>
-      <c r="D13" s="4">
-        <v>2</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="D13" s="3">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
-        <v>2</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="F13" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" s="3">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="4">
-        <v>3</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="C14" s="3">
+        <v>3</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="4">
-        <v>2</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="F14" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" s="3">
+        <v>2</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
-        <v>2</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="F15" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" s="3">
+        <v>2</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="3">
         <v>10</v>
       </c>
-      <c r="D16" s="4">
-        <v>3</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="D16" s="3">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
-        <v>2</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="F16" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" s="3">
+        <v>2</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="3">
         <v>8</v>
       </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="6">
-        <v>3</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="F17" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="4">
+        <v>3</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="6">
-        <v>2</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="C18" s="4">
+        <v>2</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="6">
-        <v>3</v>
-      </c>
-      <c r="B19" s="6" t="s">
+      <c r="F18" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="4">
+        <v>3</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="6">
-        <v>1</v>
-      </c>
-      <c r="D19" s="6">
-        <v>2</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="C19" s="4">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="6">
-        <v>3</v>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="F19" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="4">
+        <v>3</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="4">
         <v>6</v>
       </c>
-      <c r="D20" s="6">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="6">
-        <v>3</v>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="F20" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="4">
+        <v>3</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="6">
-        <v>4</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="C21" s="4">
+        <v>4</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="6">
-        <v>3</v>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="F21" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="4">
+        <v>3</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="6">
-        <v>4</v>
-      </c>
-      <c r="D22" s="6">
-        <v>2</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="C22" s="4">
+        <v>4</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="6">
-        <v>3</v>
-      </c>
-      <c r="B23" s="6" t="s">
+      <c r="F22" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="4">
+        <v>3</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="4">
         <v>7</v>
       </c>
-      <c r="D23" s="6">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="6">
-        <v>3</v>
-      </c>
-      <c r="B24" s="6" t="s">
+      <c r="F23" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" s="4">
+        <v>3</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="6">
-        <v>3</v>
-      </c>
-      <c r="D24" s="6">
-        <v>3</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4">
+        <v>3</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="6">
-        <v>3</v>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="F24" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="4">
+        <v>3</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="4">
         <v>6</v>
       </c>
-      <c r="D25" s="6">
-        <v>1</v>
-      </c>
-      <c r="E25" s="6" t="s">
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="8">
-        <v>4</v>
-      </c>
-      <c r="B26" s="8" t="s">
+      <c r="F25" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" s="5">
+        <v>4</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="5">
         <v>10</v>
       </c>
-      <c r="D26" s="8">
-        <v>1</v>
-      </c>
-      <c r="E26" s="8" t="s">
+      <c r="D26" s="5">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="8">
-        <v>4</v>
-      </c>
-      <c r="B27" s="8" t="s">
+      <c r="F26" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" s="5">
+        <v>4</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="8">
-        <v>4</v>
-      </c>
-      <c r="D27" s="8">
-        <v>1</v>
-      </c>
-      <c r="E27" s="8" t="s">
+      <c r="C27" s="5">
+        <v>4</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="8">
-        <v>4</v>
-      </c>
-      <c r="B28" s="8" t="s">
+      <c r="F27" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28" s="5">
+        <v>4</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="8">
-        <v>2</v>
-      </c>
-      <c r="D28" s="8">
-        <v>1</v>
-      </c>
-      <c r="E28" s="8" t="s">
+      <c r="C28" s="5">
+        <v>2</v>
+      </c>
+      <c r="D28" s="5">
+        <v>1</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="8">
-        <v>4</v>
-      </c>
-      <c r="B29" s="8" t="s">
+      <c r="F28" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" s="5">
+        <v>4</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="5">
         <v>6</v>
       </c>
-      <c r="D29" s="8">
-        <v>2</v>
-      </c>
-      <c r="E29" s="8" t="s">
+      <c r="D29" s="5">
+        <v>2</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="8">
-        <v>4</v>
-      </c>
-      <c r="B30" s="8" t="s">
+      <c r="F29" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" s="5">
+        <v>4</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="5">
         <v>10</v>
       </c>
-      <c r="D30" s="8">
-        <v>1</v>
-      </c>
-      <c r="E30" s="8" t="s">
+      <c r="D30" s="5">
+        <v>1</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="8">
-        <v>4</v>
-      </c>
-      <c r="B31" s="8" t="s">
+      <c r="F30" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" s="5">
+        <v>4</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="5">
         <v>8</v>
       </c>
-      <c r="D31" s="8">
-        <v>1</v>
-      </c>
-      <c r="E31" s="8" t="s">
+      <c r="D31" s="5">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F31" s="9"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="8">
-        <v>4</v>
-      </c>
-      <c r="B32" s="8" t="s">
+      <c r="F31" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" s="5">
+        <v>4</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="5">
         <v>5</v>
       </c>
-      <c r="D32" s="8">
-        <v>1</v>
-      </c>
-      <c r="E32" s="8" t="s">
+      <c r="D32" s="5">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F32" s="9"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="8">
-        <v>4</v>
-      </c>
-      <c r="B33" s="8" t="s">
+      <c r="F32" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" s="5">
+        <v>4</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="8">
-        <v>1</v>
-      </c>
-      <c r="D33" s="8">
-        <v>1</v>
-      </c>
-      <c r="E33" s="8" t="s">
+      <c r="C33" s="5">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F33" s="9"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="8">
-        <v>4</v>
-      </c>
-      <c r="B34" s="8" t="s">
+      <c r="F33" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A34" s="5">
+        <v>4</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="5">
         <v>8</v>
       </c>
-      <c r="D34" s="8">
-        <v>2</v>
-      </c>
-      <c r="E34" s="8" t="s">
+      <c r="D34" s="5">
+        <v>2</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F34" s="9"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="8">
-        <v>4</v>
-      </c>
-      <c r="B35" s="8" t="s">
+      <c r="F34" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A35" s="5">
+        <v>4</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="5">
         <v>7</v>
       </c>
-      <c r="D35" s="8">
-        <v>1</v>
-      </c>
-      <c r="E35" s="8" t="s">
+      <c r="D35" s="5">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F35" s="9"/>
+      <c r="F35" s="5" t="s">
+        <v>84</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
